--- a/outputs/58723.xlsx
+++ b/outputs/58723.xlsx
@@ -198,12 +198,9 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -230,10 +227,6 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -580,7 +573,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.67"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -621,7 +614,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
@@ -640,28 +633,28 @@
       <c r="F2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="9" t="n">
+      <c r="G2" s="7"/>
+      <c r="H2" s="8" t="n">
         <v>44176</v>
       </c>
-      <c r="I2" s="10" t="n">
+      <c r="I2" s="9" t="n">
         <v>44176.4251680556</v>
       </c>
-      <c r="J2" s="9" t="n">
+      <c r="J2" s="8" t="n">
         <v>44081</v>
       </c>
-      <c r="K2" s="9" t="n">
+      <c r="K2" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="11" t="str">
-        <f aca="false">IF(F2=1,"Latest","Not Latest")</f>
+      <c r="M2" s="10" t="str">
+        <f aca="false" t="array" ref="M2:M2">IF(I2=MAX(IF($C$2:$C$41=C2,$I$2:$I$41)),"Latest","Not Latest")</f>
         <v>Latest</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
@@ -680,28 +673,28 @@
       <c r="F3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="9" t="n">
+      <c r="G3" s="7"/>
+      <c r="H3" s="8" t="n">
         <v>44176</v>
       </c>
-      <c r="I3" s="10" t="n">
+      <c r="I3" s="9" t="n">
         <v>44176.4251680556</v>
       </c>
-      <c r="J3" s="9" t="n">
+      <c r="J3" s="8" t="n">
         <v>44081</v>
       </c>
-      <c r="K3" s="9" t="n">
+      <c r="K3" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="11" t="str">
-        <f aca="false">IF(F3=1,"Latest","Not Latest")</f>
+      <c r="M3" s="10" t="str">
+        <f aca="false" t="array" ref="M3:M3">IF(I3=MAX(IF($C$2:$C$41=C3,$I$2:$I$41)),"Latest","Not Latest")</f>
         <v>Latest</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
@@ -720,28 +713,28 @@
       <c r="F4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="9" t="n">
+      <c r="G4" s="7"/>
+      <c r="H4" s="8" t="n">
         <v>44176</v>
       </c>
-      <c r="I4" s="10" t="n">
+      <c r="I4" s="9" t="n">
         <v>44176.4251680556</v>
       </c>
-      <c r="J4" s="9" t="n">
+      <c r="J4" s="8" t="n">
         <v>44081</v>
       </c>
-      <c r="K4" s="9" t="n">
+      <c r="K4" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M4" s="11" t="str">
-        <f aca="false">IF(F4=1,"Latest","Not Latest")</f>
+      <c r="M4" s="10" t="str">
+        <f aca="false" t="array" ref="M4:M4">IF(I4=MAX(IF($C$2:$C$41=C4,$I$2:$I$41)),"Latest","Not Latest")</f>
         <v>Latest</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
@@ -760,28 +753,28 @@
       <c r="F5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="9" t="n">
+      <c r="G5" s="7"/>
+      <c r="H5" s="8" t="n">
         <v>44176</v>
       </c>
-      <c r="I5" s="10" t="n">
+      <c r="I5" s="9" t="n">
         <v>44176.4231619213</v>
       </c>
-      <c r="J5" s="9" t="n">
+      <c r="J5" s="8" t="n">
         <v>44081</v>
       </c>
-      <c r="K5" s="9" t="n">
+      <c r="K5" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M5" s="11" t="str">
-        <f aca="false">IF(F5=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M5" s="10" t="str">
+        <f aca="false" t="array" ref="M5:M5">IF(I5=MAX(IF($C$2:$C$41=C5,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
@@ -800,28 +793,28 @@
       <c r="F6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="9" t="n">
+      <c r="G6" s="7"/>
+      <c r="H6" s="8" t="n">
         <v>44176</v>
       </c>
-      <c r="I6" s="10" t="n">
+      <c r="I6" s="9" t="n">
         <v>44176.4231619213</v>
       </c>
-      <c r="J6" s="9" t="n">
+      <c r="J6" s="8" t="n">
         <v>44081</v>
       </c>
-      <c r="K6" s="9" t="n">
+      <c r="K6" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M6" s="11" t="str">
-        <f aca="false">IF(F6=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M6" s="10" t="str">
+        <f aca="false" t="array" ref="M6:M6">IF(I6=MAX(IF($C$2:$C$41=C6,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
@@ -840,28 +833,28 @@
       <c r="F7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="9" t="n">
+      <c r="G7" s="7"/>
+      <c r="H7" s="8" t="n">
         <v>44167</v>
       </c>
-      <c r="I7" s="10" t="n">
+      <c r="I7" s="9" t="n">
         <v>44167.5441532407</v>
       </c>
-      <c r="J7" s="9" t="n">
+      <c r="J7" s="8" t="n">
         <v>44081</v>
       </c>
-      <c r="K7" s="9" t="n">
+      <c r="K7" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M7" s="11" t="str">
-        <f aca="false">IF(F7=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M7" s="10" t="str">
+        <f aca="false" t="array" ref="M7:M7">IF(I7=MAX(IF($C$2:$C$41=C7,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>13</v>
       </c>
@@ -880,28 +873,28 @@
       <c r="F8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="9" t="n">
+      <c r="G8" s="7"/>
+      <c r="H8" s="8" t="n">
         <v>44167</v>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I8" s="9" t="n">
         <v>44167.5441532407</v>
       </c>
-      <c r="J8" s="9" t="n">
+      <c r="J8" s="8" t="n">
         <v>44081</v>
       </c>
-      <c r="K8" s="9" t="n">
+      <c r="K8" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="11" t="str">
-        <f aca="false">IF(F8=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M8" s="10" t="str">
+        <f aca="false" t="array" ref="M8:M8">IF(I8=MAX(IF($C$2:$C$41=C8,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
@@ -918,28 +911,28 @@
         <v>0.4</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="9" t="n">
+      <c r="G9" s="7"/>
+      <c r="H9" s="8" t="n">
         <v>44167</v>
       </c>
-      <c r="I9" s="10" t="n">
+      <c r="I9" s="9" t="n">
         <v>44167.435162963</v>
       </c>
-      <c r="J9" s="9" t="n">
+      <c r="J9" s="8" t="n">
         <v>44081</v>
       </c>
-      <c r="K9" s="9" t="n">
+      <c r="K9" s="8" t="n">
         <v>44086</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M9" s="11" t="str">
-        <f aca="false">IF(F9=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M9" s="10" t="str">
+        <f aca="false" t="array" ref="M9:M9">IF(I9=MAX(IF($C$2:$C$41=C9,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
@@ -956,28 +949,28 @@
         <v>0.5</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="9" t="n">
+      <c r="G10" s="7"/>
+      <c r="H10" s="8" t="n">
         <v>44167</v>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="I10" s="9" t="n">
         <v>44167.435162963</v>
       </c>
-      <c r="J10" s="9" t="n">
+      <c r="J10" s="8" t="n">
         <v>44081</v>
       </c>
-      <c r="K10" s="9" t="n">
+      <c r="K10" s="8" t="n">
         <v>44086</v>
       </c>
       <c r="L10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M10" s="11" t="str">
-        <f aca="false">IF(F10=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M10" s="10" t="str">
+        <f aca="false" t="array" ref="M10:M10">IF(I10=MAX(IF($C$2:$C$41=C10,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -994,28 +987,28 @@
         <v>0.1</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="9" t="n">
+      <c r="G11" s="7"/>
+      <c r="H11" s="8" t="n">
         <v>44167</v>
       </c>
-      <c r="I11" s="10" t="n">
+      <c r="I11" s="9" t="n">
         <v>44167.435162963</v>
       </c>
-      <c r="J11" s="9" t="n">
+      <c r="J11" s="8" t="n">
         <v>44081</v>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="K11" s="8" t="n">
         <v>44086</v>
       </c>
       <c r="L11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M11" s="11" t="str">
-        <f aca="false">IF(F11=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M11" s="10" t="str">
+        <f aca="false" t="array" ref="M11:M11">IF(I11=MAX(IF($C$2:$C$41=C11,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
@@ -1034,28 +1027,28 @@
       <c r="F12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="9" t="n">
+      <c r="G12" s="7"/>
+      <c r="H12" s="8" t="n">
         <v>44176</v>
       </c>
-      <c r="I12" s="10" t="n">
+      <c r="I12" s="9" t="n">
         <v>44176.4251680556</v>
       </c>
-      <c r="J12" s="9" t="n">
+      <c r="J12" s="8" t="n">
         <v>44082</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K12" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M12" s="11" t="str">
-        <f aca="false">IF(F12=1,"Latest","Not Latest")</f>
+      <c r="M12" s="10" t="str">
+        <f aca="false" t="array" ref="M12:M12">IF(I12=MAX(IF($C$2:$C$41=C12,$I$2:$I$41)),"Latest","Not Latest")</f>
         <v>Latest</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
@@ -1074,28 +1067,28 @@
       <c r="F13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="9" t="n">
+      <c r="G13" s="7"/>
+      <c r="H13" s="8" t="n">
         <v>44176</v>
       </c>
-      <c r="I13" s="10" t="n">
+      <c r="I13" s="9" t="n">
         <v>44176.4251680556</v>
       </c>
-      <c r="J13" s="9" t="n">
+      <c r="J13" s="8" t="n">
         <v>44082</v>
       </c>
-      <c r="K13" s="9" t="n">
+      <c r="K13" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="11" t="str">
-        <f aca="false">IF(F13=1,"Latest","Not Latest")</f>
+      <c r="M13" s="10" t="str">
+        <f aca="false" t="array" ref="M13:M13">IF(I13=MAX(IF($C$2:$C$41=C13,$I$2:$I$41)),"Latest","Not Latest")</f>
         <v>Latest</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
@@ -1114,28 +1107,28 @@
       <c r="F14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="9" t="n">
+      <c r="G14" s="7"/>
+      <c r="H14" s="8" t="n">
         <v>44176</v>
       </c>
-      <c r="I14" s="10" t="n">
+      <c r="I14" s="9" t="n">
         <v>44176.4251680556</v>
       </c>
-      <c r="J14" s="9" t="n">
+      <c r="J14" s="8" t="n">
         <v>44082</v>
       </c>
-      <c r="K14" s="9" t="n">
+      <c r="K14" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L14" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M14" s="11" t="str">
-        <f aca="false">IF(F14=1,"Latest","Not Latest")</f>
+      <c r="M14" s="10" t="str">
+        <f aca="false" t="array" ref="M14:M14">IF(I14=MAX(IF($C$2:$C$41=C14,$I$2:$I$41)),"Latest","Not Latest")</f>
         <v>Latest</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
@@ -1154,28 +1147,28 @@
       <c r="F15" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="9" t="n">
+      <c r="G15" s="7"/>
+      <c r="H15" s="8" t="n">
         <v>44176</v>
       </c>
-      <c r="I15" s="10" t="n">
+      <c r="I15" s="9" t="n">
         <v>44176.4231619213</v>
       </c>
-      <c r="J15" s="9" t="n">
+      <c r="J15" s="8" t="n">
         <v>44082</v>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="K15" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M15" s="11" t="str">
-        <f aca="false">IF(F15=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M15" s="10" t="str">
+        <f aca="false" t="array" ref="M15:M15">IF(I15=MAX(IF($C$2:$C$41=C15,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
         <v>13</v>
       </c>
@@ -1194,28 +1187,28 @@
       <c r="F16" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="9" t="n">
+      <c r="G16" s="7"/>
+      <c r="H16" s="8" t="n">
         <v>44176</v>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="I16" s="9" t="n">
         <v>44176.4231619213</v>
       </c>
-      <c r="J16" s="9" t="n">
+      <c r="J16" s="8" t="n">
         <v>44082</v>
       </c>
-      <c r="K16" s="9" t="n">
+      <c r="K16" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M16" s="11" t="str">
-        <f aca="false">IF(F16=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M16" s="10" t="str">
+        <f aca="false" t="array" ref="M16:M16">IF(I16=MAX(IF($C$2:$C$41=C16,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
         <v>13</v>
       </c>
@@ -1234,28 +1227,28 @@
       <c r="F17" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="9" t="n">
+      <c r="G17" s="7"/>
+      <c r="H17" s="8" t="n">
         <v>44167</v>
       </c>
-      <c r="I17" s="10" t="n">
+      <c r="I17" s="9" t="n">
         <v>44167.5441532407</v>
       </c>
-      <c r="J17" s="9" t="n">
+      <c r="J17" s="8" t="n">
         <v>44082</v>
       </c>
-      <c r="K17" s="9" t="n">
+      <c r="K17" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M17" s="11" t="str">
-        <f aca="false">IF(F17=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M17" s="10" t="str">
+        <f aca="false" t="array" ref="M17:M17">IF(I17=MAX(IF($C$2:$C$41=C17,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
@@ -1274,28 +1267,28 @@
       <c r="F18" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G18" s="8"/>
-      <c r="H18" s="9" t="n">
+      <c r="G18" s="7"/>
+      <c r="H18" s="8" t="n">
         <v>44167</v>
       </c>
-      <c r="I18" s="10" t="n">
+      <c r="I18" s="9" t="n">
         <v>44167.5441532407</v>
       </c>
-      <c r="J18" s="9" t="n">
+      <c r="J18" s="8" t="n">
         <v>44083</v>
       </c>
-      <c r="K18" s="9" t="n">
+      <c r="K18" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L18" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M18" s="11" t="str">
-        <f aca="false">IF(F18=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M18" s="10" t="str">
+        <f aca="false" t="array" ref="M18:M18">IF(I18=MAX(IF($C$2:$C$41=C18,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
         <v>13</v>
       </c>
@@ -1312,28 +1305,28 @@
         <v>0.4</v>
       </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="9" t="n">
+      <c r="G19" s="7"/>
+      <c r="H19" s="8" t="n">
         <v>44167</v>
       </c>
-      <c r="I19" s="10" t="n">
+      <c r="I19" s="9" t="n">
         <v>44167.435162963</v>
       </c>
-      <c r="J19" s="9" t="n">
+      <c r="J19" s="8" t="n">
         <v>44083</v>
       </c>
-      <c r="K19" s="9" t="n">
+      <c r="K19" s="8" t="n">
         <v>44086</v>
       </c>
       <c r="L19" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M19" s="11" t="str">
-        <f aca="false">IF(F19=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M19" s="10" t="str">
+        <f aca="false" t="array" ref="M19:M19">IF(I19=MAX(IF($C$2:$C$41=C19,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
@@ -1350,28 +1343,28 @@
         <v>0.5</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="9" t="n">
+      <c r="G20" s="7"/>
+      <c r="H20" s="8" t="n">
         <v>44167</v>
       </c>
-      <c r="I20" s="10" t="n">
+      <c r="I20" s="9" t="n">
         <v>44167.435162963</v>
       </c>
-      <c r="J20" s="9" t="n">
+      <c r="J20" s="8" t="n">
         <v>44083</v>
       </c>
-      <c r="K20" s="9" t="n">
+      <c r="K20" s="8" t="n">
         <v>44086</v>
       </c>
       <c r="L20" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M20" s="11" t="str">
-        <f aca="false">IF(F20=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M20" s="10" t="str">
+        <f aca="false" t="array" ref="M20:M20">IF(I20=MAX(IF($C$2:$C$41=C20,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
         <v>13</v>
       </c>
@@ -1388,28 +1381,28 @@
         <v>0.1</v>
       </c>
       <c r="F21" s="5"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="9" t="n">
+      <c r="G21" s="7"/>
+      <c r="H21" s="8" t="n">
         <v>44167</v>
       </c>
-      <c r="I21" s="10" t="n">
+      <c r="I21" s="9" t="n">
         <v>44167.435162963</v>
       </c>
-      <c r="J21" s="9" t="n">
+      <c r="J21" s="8" t="n">
         <v>44083</v>
       </c>
-      <c r="K21" s="9" t="n">
+      <c r="K21" s="8" t="n">
         <v>44086</v>
       </c>
       <c r="L21" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M21" s="11" t="str">
-        <f aca="false">IF(F21=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M21" s="10" t="str">
+        <f aca="false" t="array" ref="M21:M21">IF(I21=MAX(IF($C$2:$C$41=C21,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
         <v>24</v>
       </c>
@@ -1428,28 +1421,28 @@
       <c r="F22" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="8"/>
-      <c r="H22" s="9" t="n">
+      <c r="G22" s="7"/>
+      <c r="H22" s="8" t="n">
         <v>44176</v>
       </c>
-      <c r="I22" s="10" t="n">
+      <c r="I22" s="9" t="n">
         <v>44176.4251680556</v>
       </c>
-      <c r="J22" s="9" t="n">
+      <c r="J22" s="8" t="n">
         <v>44081</v>
       </c>
-      <c r="K22" s="9" t="n">
+      <c r="K22" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M22" s="11" t="str">
-        <f aca="false">IF(F22=1,"Latest","Not Latest")</f>
+      <c r="M22" s="10" t="str">
+        <f aca="false" t="array" ref="M22:M22">IF(I22=MAX(IF($C$2:$C$41=C22,$I$2:$I$41)),"Latest","Not Latest")</f>
         <v>Latest</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
         <v>24</v>
       </c>
@@ -1468,28 +1461,28 @@
       <c r="F23" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="8"/>
-      <c r="H23" s="9" t="n">
+      <c r="G23" s="7"/>
+      <c r="H23" s="8" t="n">
         <v>44176</v>
       </c>
-      <c r="I23" s="10" t="n">
+      <c r="I23" s="9" t="n">
         <v>44176.4251680556</v>
       </c>
-      <c r="J23" s="9" t="n">
+      <c r="J23" s="8" t="n">
         <v>44081</v>
       </c>
-      <c r="K23" s="9" t="n">
+      <c r="K23" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L23" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M23" s="11" t="str">
-        <f aca="false">IF(F23=1,"Latest","Not Latest")</f>
+      <c r="M23" s="10" t="str">
+        <f aca="false" t="array" ref="M23:M23">IF(I23=MAX(IF($C$2:$C$41=C23,$I$2:$I$41)),"Latest","Not Latest")</f>
         <v>Latest</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
         <v>24</v>
       </c>
@@ -1508,28 +1501,28 @@
       <c r="F24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="8"/>
-      <c r="H24" s="9" t="n">
+      <c r="G24" s="7"/>
+      <c r="H24" s="8" t="n">
         <v>44176</v>
       </c>
-      <c r="I24" s="10" t="n">
+      <c r="I24" s="9" t="n">
         <v>44176.4251680556</v>
       </c>
-      <c r="J24" s="9" t="n">
+      <c r="J24" s="8" t="n">
         <v>44081</v>
       </c>
-      <c r="K24" s="9" t="n">
+      <c r="K24" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L24" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M24" s="11" t="str">
-        <f aca="false">IF(F24=1,"Latest","Not Latest")</f>
+      <c r="M24" s="10" t="str">
+        <f aca="false" t="array" ref="M24:M24">IF(I24=MAX(IF($C$2:$C$41=C24,$I$2:$I$41)),"Latest","Not Latest")</f>
         <v>Latest</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
         <v>24</v>
       </c>
@@ -1548,28 +1541,28 @@
       <c r="F25" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G25" s="8"/>
-      <c r="H25" s="9" t="n">
+      <c r="G25" s="7"/>
+      <c r="H25" s="8" t="n">
         <v>44176</v>
       </c>
-      <c r="I25" s="10" t="n">
+      <c r="I25" s="9" t="n">
         <v>44176.4231619213</v>
       </c>
-      <c r="J25" s="9" t="n">
+      <c r="J25" s="8" t="n">
         <v>44081</v>
       </c>
-      <c r="K25" s="9" t="n">
+      <c r="K25" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M25" s="11" t="str">
-        <f aca="false">IF(F25=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M25" s="10" t="str">
+        <f aca="false" t="array" ref="M25:M25">IF(I25=MAX(IF($C$2:$C$41=C25,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
         <v>24</v>
       </c>
@@ -1588,28 +1581,28 @@
       <c r="F26" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G26" s="8"/>
-      <c r="H26" s="9" t="n">
+      <c r="G26" s="7"/>
+      <c r="H26" s="8" t="n">
         <v>44176</v>
       </c>
-      <c r="I26" s="10" t="n">
+      <c r="I26" s="9" t="n">
         <v>44176.4231619213</v>
       </c>
-      <c r="J26" s="9" t="n">
+      <c r="J26" s="8" t="n">
         <v>44081</v>
       </c>
-      <c r="K26" s="9" t="n">
+      <c r="K26" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L26" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M26" s="11" t="str">
-        <f aca="false">IF(F26=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M26" s="10" t="str">
+        <f aca="false" t="array" ref="M26:M26">IF(I26=MAX(IF($C$2:$C$41=C26,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
         <v>24</v>
       </c>
@@ -1628,28 +1621,28 @@
       <c r="F27" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G27" s="8"/>
-      <c r="H27" s="9" t="n">
+      <c r="G27" s="7"/>
+      <c r="H27" s="8" t="n">
         <v>44167</v>
       </c>
-      <c r="I27" s="10" t="n">
+      <c r="I27" s="9" t="n">
         <v>44167.5441532407</v>
       </c>
-      <c r="J27" s="9" t="n">
+      <c r="J27" s="8" t="n">
         <v>44081</v>
       </c>
-      <c r="K27" s="9" t="n">
+      <c r="K27" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L27" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M27" s="11" t="str">
-        <f aca="false">IF(F27=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M27" s="10" t="str">
+        <f aca="false" t="array" ref="M27:M27">IF(I27=MAX(IF($C$2:$C$41=C27,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
         <v>24</v>
       </c>
@@ -1668,28 +1661,28 @@
       <c r="F28" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="8"/>
-      <c r="H28" s="9" t="n">
+      <c r="G28" s="7"/>
+      <c r="H28" s="8" t="n">
         <v>44167</v>
       </c>
-      <c r="I28" s="10" t="n">
+      <c r="I28" s="9" t="n">
         <v>44167.5441532407</v>
       </c>
-      <c r="J28" s="9" t="n">
+      <c r="J28" s="8" t="n">
         <v>44081</v>
       </c>
-      <c r="K28" s="9" t="n">
+      <c r="K28" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L28" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M28" s="11" t="str">
-        <f aca="false">IF(F28=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M28" s="10" t="str">
+        <f aca="false" t="array" ref="M28:M28">IF(I28=MAX(IF($C$2:$C$41=C28,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
         <v>24</v>
       </c>
@@ -1706,28 +1699,28 @@
         <v>0.4</v>
       </c>
       <c r="F29" s="5"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="9" t="n">
+      <c r="G29" s="7"/>
+      <c r="H29" s="8" t="n">
         <v>44167</v>
       </c>
-      <c r="I29" s="10" t="n">
+      <c r="I29" s="9" t="n">
         <v>44167.435162963</v>
       </c>
-      <c r="J29" s="9" t="n">
+      <c r="J29" s="8" t="n">
         <v>44081</v>
       </c>
-      <c r="K29" s="9" t="n">
+      <c r="K29" s="8" t="n">
         <v>44086</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M29" s="11" t="str">
-        <f aca="false">IF(F29=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M29" s="10" t="str">
+        <f aca="false" t="array" ref="M29:M29">IF(I29=MAX(IF($C$2:$C$41=C29,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
         <v>24</v>
       </c>
@@ -1744,28 +1737,28 @@
         <v>0.5</v>
       </c>
       <c r="F30" s="5"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="9" t="n">
+      <c r="G30" s="7"/>
+      <c r="H30" s="8" t="n">
         <v>44167</v>
       </c>
-      <c r="I30" s="10" t="n">
+      <c r="I30" s="9" t="n">
         <v>44167.435162963</v>
       </c>
-      <c r="J30" s="9" t="n">
+      <c r="J30" s="8" t="n">
         <v>44081</v>
       </c>
-      <c r="K30" s="9" t="n">
+      <c r="K30" s="8" t="n">
         <v>44086</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M30" s="11" t="str">
-        <f aca="false">IF(F30=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M30" s="10" t="str">
+        <f aca="false" t="array" ref="M30:M30">IF(I30=MAX(IF($C$2:$C$41=C30,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
         <v>24</v>
       </c>
@@ -1782,28 +1775,28 @@
         <v>0.1</v>
       </c>
       <c r="F31" s="5"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="9" t="n">
+      <c r="G31" s="7"/>
+      <c r="H31" s="8" t="n">
         <v>44167</v>
       </c>
-      <c r="I31" s="10" t="n">
+      <c r="I31" s="9" t="n">
         <v>44167.435162963</v>
       </c>
-      <c r="J31" s="9" t="n">
+      <c r="J31" s="8" t="n">
         <v>44081</v>
       </c>
-      <c r="K31" s="9" t="n">
+      <c r="K31" s="8" t="n">
         <v>44086</v>
       </c>
       <c r="L31" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M31" s="11" t="str">
-        <f aca="false">IF(F31=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M31" s="10" t="str">
+        <f aca="false" t="array" ref="M31:M31">IF(I31=MAX(IF($C$2:$C$41=C31,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -1822,28 +1815,28 @@
       <c r="F32" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G32" s="8"/>
-      <c r="H32" s="9" t="n">
+      <c r="G32" s="7"/>
+      <c r="H32" s="8" t="n">
         <v>44176</v>
       </c>
-      <c r="I32" s="10" t="n">
+      <c r="I32" s="9" t="n">
         <v>44176.4251680556</v>
       </c>
-      <c r="J32" s="9" t="n">
+      <c r="J32" s="8" t="n">
         <v>44082</v>
       </c>
-      <c r="K32" s="9" t="n">
+      <c r="K32" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L32" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M32" s="11" t="str">
-        <f aca="false">IF(F32=1,"Latest","Not Latest")</f>
+      <c r="M32" s="10" t="str">
+        <f aca="false" t="array" ref="M32:M32">IF(I32=MAX(IF($C$2:$C$41=C32,$I$2:$I$41)),"Latest","Not Latest")</f>
         <v>Latest</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
         <v>24</v>
       </c>
@@ -1862,28 +1855,28 @@
       <c r="F33" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="8"/>
-      <c r="H33" s="9" t="n">
+      <c r="G33" s="7"/>
+      <c r="H33" s="8" t="n">
         <v>44176</v>
       </c>
-      <c r="I33" s="10" t="n">
+      <c r="I33" s="9" t="n">
         <v>44176.4251680556</v>
       </c>
-      <c r="J33" s="9" t="n">
+      <c r="J33" s="8" t="n">
         <v>44082</v>
       </c>
-      <c r="K33" s="9" t="n">
+      <c r="K33" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M33" s="11" t="str">
-        <f aca="false">IF(F33=1,"Latest","Not Latest")</f>
+      <c r="M33" s="10" t="str">
+        <f aca="false" t="array" ref="M33:M33">IF(I33=MAX(IF($C$2:$C$41=C33,$I$2:$I$41)),"Latest","Not Latest")</f>
         <v>Latest</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
         <v>24</v>
       </c>
@@ -1902,28 +1895,28 @@
       <c r="F34" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G34" s="8"/>
-      <c r="H34" s="9" t="n">
+      <c r="G34" s="7"/>
+      <c r="H34" s="8" t="n">
         <v>44176</v>
       </c>
-      <c r="I34" s="10" t="n">
+      <c r="I34" s="9" t="n">
         <v>44176.4251680556</v>
       </c>
-      <c r="J34" s="9" t="n">
+      <c r="J34" s="8" t="n">
         <v>44082</v>
       </c>
-      <c r="K34" s="9" t="n">
+      <c r="K34" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L34" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M34" s="11" t="str">
-        <f aca="false">IF(F34=1,"Latest","Not Latest")</f>
+      <c r="M34" s="10" t="str">
+        <f aca="false" t="array" ref="M34:M34">IF(I34=MAX(IF($C$2:$C$41=C34,$I$2:$I$41)),"Latest","Not Latest")</f>
         <v>Latest</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
         <v>24</v>
       </c>
@@ -1942,28 +1935,28 @@
       <c r="F35" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G35" s="8"/>
-      <c r="H35" s="9" t="n">
+      <c r="G35" s="7"/>
+      <c r="H35" s="8" t="n">
         <v>44176</v>
       </c>
-      <c r="I35" s="10" t="n">
+      <c r="I35" s="9" t="n">
         <v>44176.4231619213</v>
       </c>
-      <c r="J35" s="9" t="n">
+      <c r="J35" s="8" t="n">
         <v>44082</v>
       </c>
-      <c r="K35" s="9" t="n">
+      <c r="K35" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L35" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M35" s="11" t="str">
-        <f aca="false">IF(F35=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M35" s="10" t="str">
+        <f aca="false" t="array" ref="M35:M35">IF(I35=MAX(IF($C$2:$C$41=C35,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
         <v>24</v>
       </c>
@@ -1982,28 +1975,28 @@
       <c r="F36" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G36" s="8"/>
-      <c r="H36" s="9" t="n">
+      <c r="G36" s="7"/>
+      <c r="H36" s="8" t="n">
         <v>44176</v>
       </c>
-      <c r="I36" s="10" t="n">
+      <c r="I36" s="9" t="n">
         <v>44176.4231619213</v>
       </c>
-      <c r="J36" s="9" t="n">
+      <c r="J36" s="8" t="n">
         <v>44082</v>
       </c>
-      <c r="K36" s="9" t="n">
+      <c r="K36" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L36" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M36" s="11" t="str">
-        <f aca="false">IF(F36=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M36" s="10" t="str">
+        <f aca="false" t="array" ref="M36:M36">IF(I36=MAX(IF($C$2:$C$41=C36,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
         <v>24</v>
       </c>
@@ -2022,28 +2015,28 @@
       <c r="F37" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G37" s="8"/>
-      <c r="H37" s="9" t="n">
+      <c r="G37" s="7"/>
+      <c r="H37" s="8" t="n">
         <v>44167</v>
       </c>
-      <c r="I37" s="10" t="n">
+      <c r="I37" s="9" t="n">
         <v>44167.5441532407</v>
       </c>
-      <c r="J37" s="9" t="n">
+      <c r="J37" s="8" t="n">
         <v>44082</v>
       </c>
-      <c r="K37" s="9" t="n">
+      <c r="K37" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L37" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M37" s="11" t="str">
-        <f aca="false">IF(F37=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M37" s="10" t="str">
+        <f aca="false" t="array" ref="M37:M37">IF(I37=MAX(IF($C$2:$C$41=C37,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
         <v>24</v>
       </c>
@@ -2062,28 +2055,28 @@
       <c r="F38" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G38" s="8"/>
-      <c r="H38" s="9" t="n">
+      <c r="G38" s="7"/>
+      <c r="H38" s="8" t="n">
         <v>44167</v>
       </c>
-      <c r="I38" s="10" t="n">
+      <c r="I38" s="9" t="n">
         <v>44167.5441532407</v>
       </c>
-      <c r="J38" s="9" t="n">
+      <c r="J38" s="8" t="n">
         <v>44083</v>
       </c>
-      <c r="K38" s="9" t="n">
+      <c r="K38" s="8" t="n">
         <v>44085</v>
       </c>
       <c r="L38" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M38" s="11" t="str">
-        <f aca="false">IF(F38=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M38" s="10" t="str">
+        <f aca="false" t="array" ref="M38:M38">IF(I38=MAX(IF($C$2:$C$41=C38,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
         <v>24</v>
       </c>
@@ -2100,28 +2093,28 @@
         <v>0.4</v>
       </c>
       <c r="F39" s="5"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="9" t="n">
+      <c r="G39" s="7"/>
+      <c r="H39" s="8" t="n">
         <v>44167</v>
       </c>
-      <c r="I39" s="10" t="n">
+      <c r="I39" s="9" t="n">
         <v>44167.435162963</v>
       </c>
-      <c r="J39" s="9" t="n">
+      <c r="J39" s="8" t="n">
         <v>44083</v>
       </c>
-      <c r="K39" s="9" t="n">
+      <c r="K39" s="8" t="n">
         <v>44086</v>
       </c>
       <c r="L39" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M39" s="11" t="str">
-        <f aca="false">IF(F39=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M39" s="10" t="str">
+        <f aca="false" t="array" ref="M39:M39">IF(I39=MAX(IF($C$2:$C$41=C39,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
         <v>24</v>
       </c>
@@ -2138,28 +2131,28 @@
         <v>0.5</v>
       </c>
       <c r="F40" s="5"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="9" t="n">
+      <c r="G40" s="7"/>
+      <c r="H40" s="8" t="n">
         <v>44167</v>
       </c>
-      <c r="I40" s="10" t="n">
+      <c r="I40" s="9" t="n">
         <v>44167.435162963</v>
       </c>
-      <c r="J40" s="9" t="n">
+      <c r="J40" s="8" t="n">
         <v>44083</v>
       </c>
-      <c r="K40" s="9" t="n">
+      <c r="K40" s="8" t="n">
         <v>44086</v>
       </c>
       <c r="L40" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M40" s="11" t="str">
-        <f aca="false">IF(F40=1,"Latest","Not Latest")</f>
-        <v>Not Latest</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M40" s="10" t="str">
+        <f aca="false" t="array" ref="M40:M40">IF(I40=MAX(IF($C$2:$C$41=C40,$I$2:$I$41)),"Latest","Not Latest")</f>
+        <v>Not Latest</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
         <v>24</v>
       </c>
@@ -2176,24 +2169,24 @@
         <v>0.1</v>
       </c>
       <c r="F41" s="5"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="9" t="n">
+      <c r="G41" s="7"/>
+      <c r="H41" s="8" t="n">
         <v>44167</v>
       </c>
-      <c r="I41" s="10" t="n">
+      <c r="I41" s="9" t="n">
         <v>44167.435162963</v>
       </c>
-      <c r="J41" s="9" t="n">
+      <c r="J41" s="8" t="n">
         <v>44083</v>
       </c>
-      <c r="K41" s="9" t="n">
+      <c r="K41" s="8" t="n">
         <v>44086</v>
       </c>
       <c r="L41" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M41" s="11" t="str">
-        <f aca="false">IF(F41=1,"Latest","Not Latest")</f>
+      <c r="M41" s="10" t="str">
+        <f aca="false" t="array" ref="M41:M41">IF(I41=MAX(IF($C$2:$C$41=C41,$I$2:$I$41)),"Latest","Not Latest")</f>
         <v>Not Latest</v>
       </c>
     </row>
